--- a/Benchmark experiments-result/PFSP.xlsx
+++ b/Benchmark experiments-result/PFSP.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\11067\Desktop\Section3\GitHub上传结果\experiment2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\11067\Desktop\Section3\GitHub上传结果\Benchmark experiments-result\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0637419E-D776-483E-A3D4-589C16966968}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D74A527-D28E-43B7-A6B9-C257103B44BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51090" yWindow="-110" windowWidth="21820" windowHeight="37900" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="38596" windowHeight="21075" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TA" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">TA!#REF!</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'VRF-LARGE'!$A$1:$C$177</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -798,7 +799,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -822,16 +823,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2048,1938 +2039,1938 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="8" t="s">
         <v>229</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="2" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="5">
         <v>5831</v>
       </c>
-      <c r="C2" s="9">
+      <c r="C2" s="2">
         <v>5821</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="12">
+      <c r="B3" s="5">
         <v>5982</v>
       </c>
-      <c r="C3" s="9">
+      <c r="C3" s="2">
         <v>5998</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="12">
+      <c r="B4" s="5">
         <v>5871</v>
       </c>
-      <c r="C4" s="9">
+      <c r="C4" s="2">
         <v>5840</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="12">
+      <c r="B5" s="5">
         <v>5874</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="2">
         <v>5883</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="5">
         <v>5976</v>
       </c>
-      <c r="C6" s="9">
+      <c r="C6" s="2">
         <v>5917</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="12">
+      <c r="B7" s="5">
         <v>6009</v>
       </c>
-      <c r="C7" s="9">
+      <c r="C7" s="2">
         <v>6020</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="5">
         <v>6065</v>
       </c>
-      <c r="C8" s="9">
+      <c r="C8" s="2">
         <v>6053</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="12">
+      <c r="B9" s="5">
         <v>5813</v>
       </c>
-      <c r="C9" s="9">
+      <c r="C9" s="2">
         <v>5740</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="12">
+      <c r="B10" s="5">
         <v>5997</v>
       </c>
-      <c r="C10" s="9">
+      <c r="C10" s="2">
         <v>5977</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="5">
         <v>5870</v>
       </c>
-      <c r="C11" s="9">
+      <c r="C11" s="2">
         <v>5834</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="12">
+      <c r="B12" s="5">
         <v>6824</v>
       </c>
-      <c r="C12" s="9">
+      <c r="C12" s="2">
         <v>6700</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="12">
+      <c r="B13" s="5">
         <v>6871</v>
       </c>
-      <c r="C13" s="9">
+      <c r="C13" s="2">
         <v>6827</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="12">
+      <c r="B14" s="5">
         <v>6834</v>
       </c>
-      <c r="C14" s="9">
+      <c r="C14" s="2">
         <v>6738</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="12">
+      <c r="B15" s="5">
         <v>6860</v>
       </c>
-      <c r="C15" s="9">
+      <c r="C15" s="2">
         <v>6785</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A16" s="11" t="s">
+      <c r="A16" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="12">
+      <c r="B16" s="5">
         <v>6871</v>
       </c>
-      <c r="C16" s="12">
+      <c r="C16" s="5">
         <v>6856</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A17" s="11" t="s">
+      <c r="A17" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B17" s="12">
+      <c r="B17" s="5">
         <v>6973</v>
       </c>
-      <c r="C17" s="9">
+      <c r="C17" s="2">
         <v>6874</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="12">
+      <c r="B18" s="5">
         <v>6961</v>
       </c>
-      <c r="C18" s="9">
+      <c r="C18" s="2">
         <v>6923</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A19" s="11" t="s">
+      <c r="A19" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B19" s="12">
+      <c r="B19" s="5">
         <v>6974</v>
       </c>
-      <c r="C19" s="9">
+      <c r="C19" s="2">
         <v>6919</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A20" s="11" t="s">
+      <c r="A20" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B20" s="12">
+      <c r="B20" s="5">
         <v>6936</v>
       </c>
-      <c r="C20" s="9">
+      <c r="C20" s="2">
         <v>6820</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A21" s="11" t="s">
+      <c r="A21" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B21" s="12">
+      <c r="B21" s="5">
         <v>6869</v>
       </c>
-      <c r="C21" s="9">
+      <c r="C21" s="2">
         <v>6785</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A22" s="11" t="s">
+      <c r="A22" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B22" s="12">
+      <c r="B22" s="5">
         <v>7625</v>
       </c>
-      <c r="C22" s="9">
+      <c r="C22" s="2">
         <v>7543</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A23" s="11" t="s">
+      <c r="A23" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B23" s="12">
+      <c r="B23" s="5">
         <v>7971</v>
       </c>
-      <c r="C23" s="9">
+      <c r="C23" s="2">
         <v>7801</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A24" s="11" t="s">
+      <c r="A24" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B24" s="12">
+      <c r="B24" s="5">
         <v>7629</v>
       </c>
-      <c r="C24" s="9">
+      <c r="C24" s="2">
         <v>7652</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A25" s="11" t="s">
+      <c r="A25" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="12">
+      <c r="B25" s="5">
         <v>7770</v>
       </c>
-      <c r="C25" s="9">
+      <c r="C25" s="2">
         <v>7695</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A26" s="11" t="s">
+      <c r="A26" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="12">
+      <c r="B26" s="5">
         <v>7896</v>
       </c>
-      <c r="C26" s="9">
+      <c r="C26" s="2">
         <v>7820</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A27" s="11" t="s">
+      <c r="A27" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="12">
+      <c r="B27" s="5">
         <v>8014</v>
       </c>
-      <c r="C27" s="9">
+      <c r="C27" s="2">
         <v>7867</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A28" s="11" t="s">
+      <c r="A28" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B28" s="12">
+      <c r="B28" s="5">
         <v>7850</v>
       </c>
-      <c r="C28" s="9">
+      <c r="C28" s="2">
         <v>7801</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A29" s="11" t="s">
+      <c r="A29" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="12">
+      <c r="B29" s="5">
         <v>7981</v>
       </c>
-      <c r="C29" s="9">
+      <c r="C29" s="2">
         <v>7807</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A30" s="11" t="s">
+      <c r="A30" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="12">
+      <c r="B30" s="5">
         <v>7812</v>
       </c>
-      <c r="C30" s="9">
+      <c r="C30" s="2">
         <v>7767</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A31" s="11" t="s">
+      <c r="A31" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="12">
+      <c r="B31" s="5">
         <v>7888</v>
       </c>
-      <c r="C31" s="9">
+      <c r="C31" s="2">
         <v>7837</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A32" s="11" t="s">
+      <c r="A32" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="12">
+      <c r="B32" s="5">
         <v>10986</v>
       </c>
-      <c r="C32" s="12">
+      <c r="C32" s="5">
         <v>10967</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A33" s="11" t="s">
+      <c r="A33" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="12">
+      <c r="B33" s="5">
         <v>11121</v>
       </c>
-      <c r="C33" s="12">
+      <c r="C33" s="5">
         <v>11031</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A34" s="11" t="s">
+      <c r="A34" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B34" s="12">
+      <c r="B34" s="5">
         <v>10923</v>
       </c>
-      <c r="C34" s="12">
+      <c r="C34" s="5">
         <v>10901</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A35" s="11" t="s">
+      <c r="A35" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B35" s="12">
+      <c r="B35" s="5">
         <v>11061</v>
       </c>
-      <c r="C35" s="9">
+      <c r="C35" s="2">
         <v>11032</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A36" s="11" t="s">
+      <c r="A36" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B36" s="12">
+      <c r="B36" s="5">
         <v>10843</v>
       </c>
-      <c r="C36" s="9">
+      <c r="C36" s="2">
         <v>10853</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A37" s="11" t="s">
+      <c r="A37" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B37" s="12">
+      <c r="B37" s="5">
         <v>11938</v>
       </c>
-      <c r="C37" s="9">
+      <c r="C37" s="2">
         <v>11862</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A38" s="11" t="s">
+      <c r="A38" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B38" s="12">
+      <c r="B38" s="5">
         <v>11869</v>
       </c>
-      <c r="C38" s="9">
+      <c r="C38" s="2">
         <v>11813</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A39" s="11" t="s">
+      <c r="A39" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B39" s="12">
+      <c r="B39" s="5">
         <v>12074</v>
       </c>
-      <c r="C39" s="9">
+      <c r="C39" s="2">
         <v>11974</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A40" s="11" t="s">
+      <c r="A40" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B40" s="12">
+      <c r="B40" s="5">
         <v>12071</v>
       </c>
-      <c r="C40" s="9">
+      <c r="C40" s="2">
         <v>12055</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A41" s="11" t="s">
+      <c r="A41" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B41" s="12">
+      <c r="B41" s="5">
         <v>11852</v>
       </c>
-      <c r="C41" s="9">
+      <c r="C41" s="2">
         <v>11748</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A42" s="11" t="s">
+      <c r="A42" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B42" s="12">
+      <c r="B42" s="5">
         <v>11878</v>
       </c>
-      <c r="C42" s="9">
+      <c r="C42" s="2">
         <v>11818</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A43" s="11" t="s">
+      <c r="A43" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B43" s="12">
+      <c r="B43" s="5">
         <v>12077</v>
       </c>
-      <c r="C43" s="9">
+      <c r="C43" s="2">
         <v>11965</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A44" s="11" t="s">
+      <c r="A44" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B44" s="12">
+      <c r="B44" s="5">
         <v>11984</v>
       </c>
-      <c r="C44" s="9">
+      <c r="C44" s="2">
         <v>11904</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A45" s="11" t="s">
+      <c r="A45" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B45" s="12">
+      <c r="B45" s="5">
         <v>11924</v>
       </c>
-      <c r="C45" s="9">
+      <c r="C45" s="2">
         <v>11879</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A46" s="11" t="s">
+      <c r="A46" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="B46" s="12">
+      <c r="B46" s="5">
         <v>12062</v>
       </c>
-      <c r="C46" s="9">
+      <c r="C46" s="2">
         <v>11960</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A47" s="11" t="s">
+      <c r="A47" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="B47" s="12">
+      <c r="B47" s="5">
         <v>13077</v>
       </c>
-      <c r="C47" s="12">
+      <c r="C47" s="5">
         <v>13001</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A48" s="11" t="s">
+      <c r="A48" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="B48" s="12">
+      <c r="B48" s="5">
         <v>13002</v>
       </c>
-      <c r="C48" s="12">
+      <c r="C48" s="5">
         <v>12882</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A49" s="11" t="s">
+      <c r="A49" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="B49" s="12">
+      <c r="B49" s="5">
         <v>13177</v>
       </c>
-      <c r="C49" s="12">
+      <c r="C49" s="5">
         <v>13050</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A50" s="11" t="s">
+      <c r="A50" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B50" s="12">
+      <c r="B50" s="5">
         <v>13024</v>
       </c>
-      <c r="C50" s="9">
+      <c r="C50" s="2">
         <v>13005</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A51" s="11" t="s">
+      <c r="A51" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="B51" s="12">
+      <c r="B51" s="5">
         <v>13244</v>
       </c>
-      <c r="C51" s="9">
+      <c r="C51" s="2">
         <v>13065</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A52" s="11" t="s">
+      <c r="A52" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B52" s="12">
+      <c r="B52" s="5">
         <v>13122</v>
       </c>
-      <c r="C52" s="9">
+      <c r="C52" s="2">
         <v>12983</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A53" s="11" t="s">
+      <c r="A53" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B53" s="12">
+      <c r="B53" s="5">
         <v>13079</v>
       </c>
-      <c r="C53" s="9">
+      <c r="C53" s="2">
         <v>13011</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A54" s="11" t="s">
+      <c r="A54" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="B54" s="12">
+      <c r="B54" s="5">
         <v>13075</v>
       </c>
-      <c r="C54" s="9">
+      <c r="C54" s="2">
         <v>12992</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A55" s="11" t="s">
+      <c r="A55" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B55" s="12">
+      <c r="B55" s="5">
         <v>13029</v>
       </c>
-      <c r="C55" s="9">
+      <c r="C55" s="2">
         <v>12958</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A56" s="11" t="s">
+      <c r="A56" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="B56" s="12">
+      <c r="B56" s="5">
         <v>13054</v>
       </c>
-      <c r="C56" s="9">
+      <c r="C56" s="2">
         <v>12940</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A57" s="11" t="s">
+      <c r="A57" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B57" s="12">
+      <c r="B57" s="5">
         <v>16922</v>
       </c>
-      <c r="C57" s="12">
+      <c r="C57" s="5">
         <v>17014</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A58" s="11" t="s">
+      <c r="A58" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B58" s="12">
+      <c r="B58" s="5">
         <v>17101</v>
       </c>
-      <c r="C58" s="12">
+      <c r="C58" s="5">
         <v>17095</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A59" s="11" t="s">
+      <c r="A59" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="B59" s="12">
+      <c r="B59" s="5">
         <v>17109</v>
       </c>
-      <c r="C59" s="12">
+      <c r="C59" s="5">
         <v>17009</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A60" s="11" t="s">
+      <c r="A60" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="B60" s="12">
+      <c r="B60" s="5">
         <v>17000</v>
       </c>
-      <c r="C60" s="9">
+      <c r="C60" s="2">
         <v>16937</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A61" s="11" t="s">
+      <c r="A61" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B61" s="12">
+      <c r="B61" s="5">
         <v>17183</v>
       </c>
-      <c r="C61" s="9">
+      <c r="C61" s="2">
         <v>17128</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A62" s="11" t="s">
+      <c r="A62" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="B62" s="12">
+      <c r="B62" s="5">
         <v>17086</v>
       </c>
-      <c r="C62" s="9">
+      <c r="C62" s="2">
         <v>17010</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A63" s="11" t="s">
+      <c r="A63" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="B63" s="12">
+      <c r="B63" s="5">
         <v>17156</v>
       </c>
-      <c r="C63" s="9">
+      <c r="C63" s="2">
         <v>17079</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A64" s="11" t="s">
+      <c r="A64" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="B64" s="12">
+      <c r="B64" s="5">
         <v>17118</v>
       </c>
-      <c r="C64" s="9">
+      <c r="C64" s="2">
         <v>17078</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A65" s="11" t="s">
+      <c r="A65" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="B65" s="12">
+      <c r="B65" s="5">
         <v>17115</v>
       </c>
-      <c r="C65" s="9">
+      <c r="C65" s="2">
         <v>17085</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A66" s="11" t="s">
+      <c r="A66" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="B66" s="12">
+      <c r="B66" s="5">
         <v>17098</v>
       </c>
-      <c r="C66" s="9">
+      <c r="C66" s="2">
         <v>18102</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A67" s="11" t="s">
+      <c r="A67" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="B67" s="12">
+      <c r="B67" s="5">
         <v>18132</v>
       </c>
-      <c r="C67" s="9">
+      <c r="C67" s="2">
         <v>18102</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A68" s="11" t="s">
+      <c r="A68" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="B68" s="12">
+      <c r="B68" s="5">
         <v>17973</v>
       </c>
-      <c r="C68" s="12">
+      <c r="C68" s="5">
         <v>17822</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A69" s="11" t="s">
+      <c r="A69" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="B69" s="12">
+      <c r="B69" s="5">
         <v>18140</v>
       </c>
-      <c r="C69" s="9">
+      <c r="C69" s="2">
         <v>18155</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A70" s="11" t="s">
+      <c r="A70" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="B70" s="12">
+      <c r="B70" s="5">
         <v>18031</v>
       </c>
-      <c r="C70" s="12">
+      <c r="C70" s="5">
         <v>17990</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A71" s="11" t="s">
+      <c r="A71" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="B71" s="12">
+      <c r="B71" s="5">
         <v>18012</v>
       </c>
-      <c r="C71" s="9">
+      <c r="C71" s="2">
         <v>17892</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A72" s="11" t="s">
+      <c r="A72" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="B72" s="12">
+      <c r="B72" s="5">
         <v>17948</v>
       </c>
-      <c r="C72" s="12">
+      <c r="C72" s="5">
         <v>17909</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A73" s="11" t="s">
+      <c r="A73" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="B73" s="12">
+      <c r="B73" s="5">
         <v>18213</v>
       </c>
-      <c r="C73" s="9">
+      <c r="C73" s="2">
         <v>18098</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A74" s="11" t="s">
+      <c r="A74" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="B74" s="12">
+      <c r="B74" s="5">
         <v>18120</v>
       </c>
-      <c r="C74" s="12">
+      <c r="C74" s="5">
         <v>18037</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A75" s="11" t="s">
+      <c r="A75" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="B75" s="12">
+      <c r="B75" s="5">
         <v>18178</v>
       </c>
-      <c r="C75" s="12">
+      <c r="C75" s="5">
         <v>18029</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A76" s="11" t="s">
+      <c r="A76" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="B76" s="12">
+      <c r="B76" s="5">
         <v>18084</v>
       </c>
-      <c r="C76" s="12">
+      <c r="C76" s="5">
         <v>17977</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A77" s="11" t="s">
+      <c r="A77" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="B77" s="12">
+      <c r="B77" s="5">
         <v>22159</v>
       </c>
-      <c r="C77" s="9">
+      <c r="C77" s="2">
         <v>22099</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A78" s="11" t="s">
+      <c r="A78" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="B78" s="12">
+      <c r="B78" s="5">
         <v>22000</v>
       </c>
-      <c r="C78" s="12">
+      <c r="C78" s="5">
         <v>21917</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A79" s="11" t="s">
+      <c r="A79" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="B79" s="12">
+      <c r="B79" s="5">
         <v>22283</v>
       </c>
-      <c r="C79" s="9">
+      <c r="C79" s="2">
         <v>22154</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A80" s="11" t="s">
+      <c r="A80" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="B80" s="12">
+      <c r="B80" s="5">
         <v>21984</v>
       </c>
-      <c r="C80" s="12">
+      <c r="C80" s="5">
         <v>21967</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A81" s="11" t="s">
+      <c r="A81" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="B81" s="12">
+      <c r="B81" s="5">
         <v>21987</v>
       </c>
-      <c r="C81" s="9">
+      <c r="C81" s="2">
         <v>21931</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A82" s="11" t="s">
+      <c r="A82" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="B82" s="12">
+      <c r="B82" s="5">
         <v>22083</v>
       </c>
-      <c r="C82" s="12">
+      <c r="C82" s="5">
         <v>22043</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A83" s="11" t="s">
+      <c r="A83" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="B83" s="12">
+      <c r="B83" s="5">
         <v>22258</v>
       </c>
-      <c r="C83" s="9">
+      <c r="C83" s="2">
         <v>22145</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A84" s="11" t="s">
+      <c r="A84" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="B84" s="12">
+      <c r="B84" s="5">
         <v>22030</v>
       </c>
-      <c r="C84" s="12">
+      <c r="C84" s="5">
         <v>21924</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A85" s="11" t="s">
+      <c r="A85" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="B85" s="12">
+      <c r="B85" s="5">
         <v>22236</v>
       </c>
-      <c r="C85" s="9">
+      <c r="C85" s="2">
         <v>22177</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A86" s="11" t="s">
+      <c r="A86" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="B86" s="12">
+      <c r="B86" s="5">
         <v>22416</v>
       </c>
-      <c r="C86" s="9">
+      <c r="C86" s="2">
         <v>22301</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A87" s="11" t="s">
+      <c r="A87" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="B87" s="12">
+      <c r="B87" s="5">
         <v>23009</v>
       </c>
-      <c r="C87" s="12">
+      <c r="C87" s="5">
         <v>22927</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A88" s="11" t="s">
+      <c r="A88" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="B88" s="12">
+      <c r="B88" s="5">
         <v>23018</v>
       </c>
-      <c r="C88" s="12">
+      <c r="C88" s="5">
         <v>22914</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A89" s="11" t="s">
+      <c r="A89" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="B89" s="12">
+      <c r="B89" s="5">
         <v>23224</v>
       </c>
-      <c r="C89" s="9">
+      <c r="C89" s="2">
         <v>23161</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A90" s="11" t="s">
+      <c r="A90" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="B90" s="12">
+      <c r="B90" s="5">
         <v>23239</v>
       </c>
-      <c r="C90" s="12">
+      <c r="C90" s="5">
         <v>23150</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A91" s="11" t="s">
+      <c r="A91" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="B91" s="12">
+      <c r="B91" s="5">
         <v>23143</v>
       </c>
-      <c r="C91" s="12">
+      <c r="C91" s="5">
         <v>23140</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A92" s="11" t="s">
+      <c r="A92" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="B92" s="12">
+      <c r="B92" s="5">
         <v>22990</v>
       </c>
-      <c r="C92" s="9">
+      <c r="C92" s="2">
         <v>22861</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A93" s="11" t="s">
+      <c r="A93" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="B93" s="12">
+      <c r="B93" s="5">
         <v>23078</v>
       </c>
-      <c r="C93" s="9">
+      <c r="C93" s="2">
         <v>23022</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A94" s="11" t="s">
+      <c r="A94" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="B94" s="12">
+      <c r="B94" s="5">
         <v>23253</v>
       </c>
-      <c r="C94" s="9">
+      <c r="C94" s="2">
         <v>23127</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A95" s="11" t="s">
+      <c r="A95" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="B95" s="12">
+      <c r="B95" s="5">
         <v>23322</v>
       </c>
-      <c r="C95" s="9">
+      <c r="C95" s="2">
         <v>23269</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A96" s="11" t="s">
+      <c r="A96" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="B96" s="12">
+      <c r="B96" s="5">
         <v>23288</v>
       </c>
-      <c r="C96" s="9">
+      <c r="C96" s="2">
         <v>23245</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A97" s="11" t="s">
+      <c r="A97" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="B97" s="12">
+      <c r="B97" s="5">
         <v>27094</v>
       </c>
-      <c r="C97" s="12">
+      <c r="C97" s="5">
         <v>27076</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A98" s="11" t="s">
+      <c r="A98" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="B98" s="12">
+      <c r="B98" s="5">
         <v>27331</v>
       </c>
-      <c r="C98" s="9">
+      <c r="C98" s="2">
         <v>27208</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A99" s="11" t="s">
+      <c r="A99" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="B99" s="12">
+      <c r="B99" s="5">
         <v>27121</v>
       </c>
-      <c r="C99" s="12">
+      <c r="C99" s="5">
         <v>27113</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A100" s="11" t="s">
+      <c r="A100" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="B100" s="12">
+      <c r="B100" s="5">
         <v>27329</v>
       </c>
-      <c r="C100" s="9">
+      <c r="C100" s="2">
         <v>27255</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A101" s="11" t="s">
+      <c r="A101" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="B101" s="12">
+      <c r="B101" s="5">
         <v>27258</v>
       </c>
-      <c r="C101" s="9">
+      <c r="C101" s="2">
         <v>27140</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A102" s="11" t="s">
+      <c r="A102" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="B102" s="12">
+      <c r="B102" s="5">
         <v>27084</v>
       </c>
-      <c r="C102" s="9">
+      <c r="C102" s="2">
         <v>26950</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A103" s="11" t="s">
+      <c r="A103" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="B103" s="12">
+      <c r="B103" s="5">
         <v>27259</v>
       </c>
-      <c r="C103" s="9">
+      <c r="C103" s="2">
         <v>27183</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A104" s="11" t="s">
+      <c r="A104" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="B104" s="12">
+      <c r="B104" s="5">
         <v>27426</v>
       </c>
-      <c r="C104" s="12">
+      <c r="C104" s="5">
         <v>27257</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A105" s="11" t="s">
+      <c r="A105" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="B105" s="12">
+      <c r="B105" s="5">
         <v>27412</v>
       </c>
-      <c r="C105" s="9">
+      <c r="C105" s="2">
         <v>27336</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A106" s="11" t="s">
+      <c r="A106" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="B106" s="12">
+      <c r="B106" s="5">
         <v>27361</v>
       </c>
-      <c r="C106" s="9">
+      <c r="C106" s="2">
         <v>27269</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A107" s="11" t="s">
+      <c r="A107" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="B107" s="12">
+      <c r="B107" s="5">
         <v>28035</v>
       </c>
-      <c r="C107" s="12">
+      <c r="C107" s="5">
         <v>27992</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A108" s="11" t="s">
+      <c r="A108" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="B108" s="12">
+      <c r="B108" s="5">
         <v>28090</v>
       </c>
-      <c r="C108" s="12">
+      <c r="C108" s="5">
         <v>27927</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A109" s="11" t="s">
+      <c r="A109" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="B109" s="12">
+      <c r="B109" s="5">
         <v>28220</v>
       </c>
-      <c r="C109" s="12">
+      <c r="C109" s="5">
         <v>28138</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A110" s="11" t="s">
+      <c r="A110" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="B110" s="12">
+      <c r="B110" s="5">
         <v>28234</v>
       </c>
-      <c r="C110" s="12">
+      <c r="C110" s="5">
         <v>28079</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A111" s="11" t="s">
+      <c r="A111" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="B111" s="12">
+      <c r="B111" s="5">
         <v>28159</v>
       </c>
-      <c r="C111" s="9">
+      <c r="C111" s="2">
         <v>28064</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A112" s="11" t="s">
+      <c r="A112" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="B112" s="12">
+      <c r="B112" s="5">
         <v>28197</v>
       </c>
-      <c r="C112" s="12">
+      <c r="C112" s="5">
         <v>28189</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A113" s="11" t="s">
+      <c r="A113" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="B113" s="12">
+      <c r="B113" s="5">
         <v>28208</v>
       </c>
-      <c r="C113" s="9">
+      <c r="C113" s="2">
         <v>28231</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A114" s="11" t="s">
+      <c r="A114" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="B114" s="12">
+      <c r="B114" s="5">
         <v>28368</v>
       </c>
-      <c r="C114" s="12">
+      <c r="C114" s="5">
         <v>28182</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A115" s="11" t="s">
+      <c r="A115" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="B115" s="12">
+      <c r="B115" s="5">
         <v>28298</v>
       </c>
-      <c r="C115" s="12">
+      <c r="C115" s="5">
         <v>28154</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A116" s="11" t="s">
+      <c r="A116" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="B116" s="12">
+      <c r="B116" s="5">
         <v>28399</v>
       </c>
-      <c r="C116" s="9">
+      <c r="C116" s="2">
         <v>28264</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A117" s="11" t="s">
+      <c r="A117" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="B117" s="12">
+      <c r="B117" s="5">
         <v>32396</v>
       </c>
-      <c r="C117" s="9">
+      <c r="C117" s="2">
         <v>32305</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A118" s="11" t="s">
+      <c r="A118" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="B118" s="12">
+      <c r="B118" s="5">
         <v>32228</v>
       </c>
-      <c r="C118" s="9">
+      <c r="C118" s="2">
         <v>32214</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A119" s="11" t="s">
+      <c r="A119" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="B119" s="12">
+      <c r="B119" s="5">
         <v>32419</v>
       </c>
-      <c r="C119" s="9">
+      <c r="C119" s="2">
         <v>32341</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A120" s="11" t="s">
+      <c r="A120" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="B120" s="12">
+      <c r="B120" s="5">
         <v>32304</v>
       </c>
-      <c r="C120" s="9">
+      <c r="C120" s="2">
         <v>32226</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A121" s="11" t="s">
+      <c r="A121" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="B121" s="12">
+      <c r="B121" s="5">
         <v>32163</v>
       </c>
-      <c r="C121" s="9">
+      <c r="C121" s="2">
         <v>32101</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A122" s="11" t="s">
+      <c r="A122" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="B122" s="12">
+      <c r="B122" s="5">
         <v>32462</v>
       </c>
-      <c r="C122" s="9">
+      <c r="C122" s="2">
         <v>32352</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A123" s="11" t="s">
+      <c r="A123" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="B123" s="12">
+      <c r="B123" s="5">
         <v>32346</v>
       </c>
-      <c r="C123" s="12">
+      <c r="C123" s="5">
         <v>32263</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A124" s="11" t="s">
+      <c r="A124" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="B124" s="12">
+      <c r="B124" s="5">
         <v>32087</v>
       </c>
-      <c r="C124" s="12">
+      <c r="C124" s="5">
         <v>32108</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A125" s="11" t="s">
+      <c r="A125" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="B125" s="12">
+      <c r="B125" s="5">
         <v>32375</v>
       </c>
-      <c r="C125" s="12">
+      <c r="C125" s="5">
         <v>32318</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A126" s="11" t="s">
+      <c r="A126" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="B126" s="12">
+      <c r="B126" s="5">
         <v>32370</v>
       </c>
-      <c r="C126" s="9">
+      <c r="C126" s="2">
         <v>32257</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A127" s="11" t="s">
+      <c r="A127" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="B127" s="12">
+      <c r="B127" s="5">
         <v>33209</v>
       </c>
-      <c r="C127" s="9">
+      <c r="C127" s="2">
         <v>33159</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A128" s="11" t="s">
+      <c r="A128" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="B128" s="12">
+      <c r="B128" s="5">
         <v>33285</v>
       </c>
-      <c r="C128" s="9">
+      <c r="C128" s="2">
         <v>33196</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A129" s="11" t="s">
+      <c r="A129" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="B129" s="12">
+      <c r="B129" s="5">
         <v>33348</v>
       </c>
-      <c r="C129" s="9">
+      <c r="C129" s="2">
         <v>33179</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A130" s="11" t="s">
+      <c r="A130" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="B130" s="12">
+      <c r="B130" s="5">
         <v>33392</v>
       </c>
-      <c r="C130" s="9">
+      <c r="C130" s="2">
         <v>33290</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A131" s="11" t="s">
+      <c r="A131" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="B131" s="12">
+      <c r="B131" s="5">
         <v>33302</v>
       </c>
-      <c r="C131" s="9">
+      <c r="C131" s="2">
         <v>33160</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A132" s="11" t="s">
+      <c r="A132" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="B132" s="12">
+      <c r="B132" s="5">
         <v>33339</v>
       </c>
-      <c r="C132" s="9">
+      <c r="C132" s="2">
         <v>33235</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A133" s="11" t="s">
+      <c r="A133" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="B133" s="12">
+      <c r="B133" s="5">
         <v>33370</v>
       </c>
-      <c r="C133" s="9">
+      <c r="C133" s="2">
         <v>33354</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A134" s="11" t="s">
+      <c r="A134" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="B134" s="12">
+      <c r="B134" s="5">
         <v>33337</v>
       </c>
-      <c r="C134" s="9">
+      <c r="C134" s="2">
         <v>33290</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A135" s="11" t="s">
+      <c r="A135" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="B135" s="12">
+      <c r="B135" s="5">
         <v>33451</v>
       </c>
-      <c r="C135" s="9">
+      <c r="C135" s="2">
         <v>33321</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A136" s="11" t="s">
+      <c r="A136" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="B136" s="12">
+      <c r="B136" s="5">
         <v>33402</v>
       </c>
-      <c r="C136" s="9">
+      <c r="C136" s="2">
         <v>33258</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A137" s="11" t="s">
+      <c r="A137" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="B137" s="12">
+      <c r="B137" s="5">
         <v>37527</v>
       </c>
-      <c r="C137" s="12">
+      <c r="C137" s="5">
         <v>37364</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A138" s="11" t="s">
+      <c r="A138" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="B138" s="12">
+      <c r="B138" s="5">
         <v>37348</v>
       </c>
-      <c r="C138" s="12">
+      <c r="C138" s="5">
         <v>37283</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A139" s="11" t="s">
+      <c r="A139" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="B139" s="12">
+      <c r="B139" s="5">
         <v>37169</v>
       </c>
-      <c r="C139" s="9">
+      <c r="C139" s="2">
         <v>37088</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A140" s="11" t="s">
+      <c r="A140" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="B140" s="12">
+      <c r="B140" s="5">
         <v>37404</v>
       </c>
-      <c r="C140" s="9">
+      <c r="C140" s="2">
         <v>37276</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A141" s="11" t="s">
+      <c r="A141" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="B141" s="12">
+      <c r="B141" s="5">
         <v>37356</v>
       </c>
-      <c r="C141" s="9">
+      <c r="C141" s="2">
         <v>37234</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A142" s="11" t="s">
+      <c r="A142" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="B142" s="12">
+      <c r="B142" s="5">
         <v>37341</v>
       </c>
-      <c r="C142" s="9">
+      <c r="C142" s="2">
         <v>37249</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A143" s="11" t="s">
+      <c r="A143" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="B143" s="12">
+      <c r="B143" s="5">
         <v>37042</v>
       </c>
-      <c r="C143" s="9">
+      <c r="C143" s="2">
         <v>36994</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A144" s="11" t="s">
+      <c r="A144" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="B144" s="12">
+      <c r="B144" s="5">
         <v>37694</v>
       </c>
-      <c r="C144" s="9">
+      <c r="C144" s="2">
         <v>37566</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A145" s="11" t="s">
+      <c r="A145" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="B145" s="12">
+      <c r="B145" s="5">
         <v>37386</v>
       </c>
-      <c r="C145" s="9">
+      <c r="C145" s="2">
         <v>37274</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A146" s="11" t="s">
+      <c r="A146" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="B146" s="12">
+      <c r="B146" s="5">
         <v>37492</v>
       </c>
-      <c r="C146" s="9">
+      <c r="C146" s="2">
         <v>37479</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A147" s="11" t="s">
+      <c r="A147" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="B147" s="12">
+      <c r="B147" s="5">
         <v>38429</v>
       </c>
-      <c r="C147" s="12">
+      <c r="C147" s="5">
         <v>38289</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A148" s="11" t="s">
+      <c r="A148" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="B148" s="12">
+      <c r="B148" s="5">
         <v>38458</v>
       </c>
-      <c r="C148" s="12">
+      <c r="C148" s="5">
         <v>38300</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A149" s="11" t="s">
+      <c r="A149" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B149" s="12">
+      <c r="B149" s="5">
         <v>38321</v>
       </c>
-      <c r="C149" s="12">
+      <c r="C149" s="5">
         <v>38301</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A150" s="11" t="s">
+      <c r="A150" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="B150" s="12">
+      <c r="B150" s="5">
         <v>38603</v>
       </c>
-      <c r="C150" s="9">
+      <c r="C150" s="2">
         <v>38515</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A151" s="11" t="s">
+      <c r="A151" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="B151" s="12">
+      <c r="B151" s="5">
         <v>38454</v>
       </c>
-      <c r="C151" s="9">
+      <c r="C151" s="2">
         <v>38338</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A152" s="11" t="s">
+      <c r="A152" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="B152" s="12">
+      <c r="B152" s="5">
         <v>38427</v>
       </c>
-      <c r="C152" s="9">
+      <c r="C152" s="2">
         <v>38319</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A153" s="11" t="s">
+      <c r="A153" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="B153" s="12">
+      <c r="B153" s="5">
         <v>38115</v>
       </c>
-      <c r="C153" s="9">
+      <c r="C153" s="2">
         <v>37932</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A154" s="11" t="s">
+      <c r="A154" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="B154" s="12">
+      <c r="B154" s="5">
         <v>38593</v>
       </c>
-      <c r="C154" s="9">
+      <c r="C154" s="2">
         <v>38487</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A155" s="11" t="s">
+      <c r="A155" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="B155" s="12">
+      <c r="B155" s="5">
         <v>38375</v>
       </c>
-      <c r="C155" s="9">
+      <c r="C155" s="2">
         <v>38236</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A156" s="11" t="s">
+      <c r="A156" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="B156" s="12">
+      <c r="B156" s="5">
         <v>38488</v>
       </c>
-      <c r="C156" s="9">
+      <c r="C156" s="2">
         <v>38429</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A157" s="11" t="s">
+      <c r="A157" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="B157" s="12">
+      <c r="B157" s="5">
         <v>42307</v>
       </c>
-      <c r="C157" s="12">
+      <c r="C157" s="5">
         <v>42211</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A158" s="11" t="s">
+      <c r="A158" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="B158" s="12">
+      <c r="B158" s="5">
         <v>42238</v>
       </c>
-      <c r="C158" s="12">
+      <c r="C158" s="5">
         <v>42224</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A159" s="11" t="s">
+      <c r="A159" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="B159" s="12">
+      <c r="B159" s="5">
         <v>42255</v>
       </c>
-      <c r="C159" s="12">
+      <c r="C159" s="5">
         <v>42190</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A160" s="11" t="s">
+      <c r="A160" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="B160" s="12">
+      <c r="B160" s="5">
         <v>42473</v>
       </c>
-      <c r="C160" s="9">
+      <c r="C160" s="2">
         <v>42389</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A161" s="11" t="s">
+      <c r="A161" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="B161" s="12">
+      <c r="B161" s="5">
         <v>42586</v>
       </c>
-      <c r="C161" s="9">
+      <c r="C161" s="2">
         <v>42492</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A162" s="11" t="s">
+      <c r="A162" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="B162" s="12">
+      <c r="B162" s="5">
         <v>42272</v>
       </c>
-      <c r="C162" s="9">
+      <c r="C162" s="2">
         <v>42261</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A163" s="11" t="s">
+      <c r="A163" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="B163" s="12">
+      <c r="B163" s="5">
         <v>42369</v>
       </c>
-      <c r="C163" s="9">
+      <c r="C163" s="2">
         <v>42244</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A164" s="11" t="s">
+      <c r="A164" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="B164" s="12">
+      <c r="B164" s="5">
         <v>42551</v>
       </c>
-      <c r="C164" s="9">
+      <c r="C164" s="2">
         <v>42409</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A165" s="11" t="s">
+      <c r="A165" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="B165" s="12">
+      <c r="B165" s="5">
         <v>42458</v>
       </c>
-      <c r="C165" s="9">
+      <c r="C165" s="2">
         <v>42380</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A166" s="11" t="s">
+      <c r="A166" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="B166" s="12">
+      <c r="B166" s="5">
         <v>42523</v>
       </c>
-      <c r="C166" s="9">
+      <c r="C166" s="2">
         <v>42409</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A167" s="11" t="s">
+      <c r="A167" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="B167" s="12">
+      <c r="B167" s="5">
         <v>43412</v>
       </c>
-      <c r="C167" s="12">
+      <c r="C167" s="5">
         <v>43276</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A168" s="11" t="s">
+      <c r="A168" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="B168" s="12">
+      <c r="B168" s="5">
         <v>43307</v>
       </c>
-      <c r="C168" s="12">
-        <v>43224</v>
+      <c r="C168" s="5">
+        <v>43324</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A169" s="11" t="s">
+      <c r="A169" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="B169" s="12">
+      <c r="B169" s="5">
         <v>43370</v>
       </c>
-      <c r="C169" s="12">
+      <c r="C169" s="5">
         <v>43339</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A170" s="11" t="s">
+      <c r="A170" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="B170" s="12">
+      <c r="B170" s="5">
         <v>43371</v>
       </c>
-      <c r="C170" s="9">
+      <c r="C170" s="2">
         <v>43289</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A171" s="11" t="s">
+      <c r="A171" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="B171" s="12">
+      <c r="B171" s="5">
         <v>43369</v>
       </c>
-      <c r="C171" s="9">
+      <c r="C171" s="2">
         <v>43376</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A172" s="11" t="s">
+      <c r="A172" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="B172" s="12">
+      <c r="B172" s="5">
         <v>43397</v>
       </c>
-      <c r="C172" s="9">
+      <c r="C172" s="2">
         <v>43256</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A173" s="11" t="s">
+      <c r="A173" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="B173" s="12">
+      <c r="B173" s="5">
         <v>43407</v>
       </c>
-      <c r="C173" s="9">
+      <c r="C173" s="2">
         <v>43253</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A174" s="11" t="s">
+      <c r="A174" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="B174" s="12">
+      <c r="B174" s="5">
         <v>43478</v>
       </c>
-      <c r="C174" s="9">
+      <c r="C174" s="2">
         <v>43390</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A175" s="11" t="s">
+      <c r="A175" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="B175" s="12">
+      <c r="B175" s="5">
         <v>43642</v>
       </c>
-      <c r="C175" s="9">
+      <c r="C175" s="2">
         <v>43350</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A176" s="11" t="s">
+      <c r="A176" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="B176" s="12">
+      <c r="B176" s="5">
         <v>43459</v>
       </c>
-      <c r="C176" s="9">
+      <c r="C176" s="2">
         <v>43333</v>
       </c>
     </row>
